--- a/laboratory_forms/005_ftir_equipment_usage_survey--laboratory_forms.xlsx
+++ b/laboratory_forms/005_ftir_equipment_usage_survey--laboratory_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>satisfaction_scale</t>
+          <t>satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Satisfaction Level</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>improvement_feedback</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Improvement Feedback</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>submission_tracking</t>
+          <t>instrument_usage_frequency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Submission Tracking</t>
+          <t>Instrument Usage Frequency</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>training_needs_additional</t>
+          <t>submission_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Training Needs</t>
+          <t>Submission Status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>satisfaction_scale_2</t>
+          <t>additional_instruments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Additional Instruments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Form Submit</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Submission Time</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>instrument_usage_frequency</t>
+          <t>form_status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Instrument Usage Frequency</t>
+          <t>Form Status</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>training_needs_2</t>
+          <t>instrument_usage_frequency_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Training Needs 2</t>
+          <t>Instrument Usage Frequency 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>satisfaction_scale_3</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>instrument_used_additional</t>
+          <t>submission_user</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Instrument Used</t>
+          <t>Submission User</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>form_submit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Form Submit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>submission_time_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submission Time</t>
+          <t>Submission Time 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_status</t>
+          <t>training_needs_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Form Status</t>
+          <t>Training Needs 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>instrument_usage_frequency_2</t>
+          <t>instrument_used_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Instrument Usage Frequency 2</t>
+          <t>Instrument Used 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submission_user</t>
+          <t>submission_status_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Submission User</t>
+          <t>Submission Status 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>instrument_usage_frequency_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Instrument Usage Frequency 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,136 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>submission_user_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Form Submit</t>
+          <t>Submission User 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>training_needs_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Training Needs 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submission_time_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submission Time 2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>instrument_used_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Instrument Used 2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_status_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Form Status 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission_user_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission User 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1194,153 +1079,153 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>basic</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>5-6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>training_needs_additional_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>7-8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>training_needs_additional_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9-10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_submit_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_submit_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_submit_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>instrument_usage_frequency_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1369,148 +1254,148 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>training_needs_2_choices</t>
+          <t>instrument_usage_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>basic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>training_needs_2_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>training_needs_2_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>instrument_used_additional_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>instrument_used_additional_choices</t>
+          <t>additional_instruments_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ft-ir</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FT-IR</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>instrument_used_additional_choices</t>
+          <t>additional_instruments_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>raman</t>
+          <t>ft-ir</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>FT-IR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>instrument_used_additional_choices</t>
+          <t>additional_instruments_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nmr</t>
+          <t>raman</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>Raman</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>form_status_choices</t>
+          <t>additional_instruments_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>nmr</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>NMR</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1424,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>instrument_usage_frequency_2_choices</t>
+          <t>form_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1475,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>form_submit_choices</t>
+          <t>instrument_usage_frequency_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1509,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1641,97 +1526,97 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>training_needs_3_choices</t>
+          <t>form_submit_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>basic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>training_needs_3_choices</t>
+          <t>training_needs_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>training_needs_3_choices</t>
+          <t>training_needs_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>instrument_used_2_choices</t>
+          <t>training_needs_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ft-ir</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FT-IR</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>instrument_used_2_choices</t>
+          <t>training_needs_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>raman</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1743,63 +1628,165 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nmr</t>
+          <t>ft-ir</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>FT-IR</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>form_status_2_choices</t>
+          <t>instrument_used_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>raman</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Raman</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>form_status_2_choices</t>
+          <t>instrument_used_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>nmr</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>NMR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>form_status_2_choices</t>
+          <t>instrument_used_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>submission_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>submission_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>submission_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>instrument_usage_frequency_3_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>instrument_usage_frequency_3_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>instrument_usage_frequency_3_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
